--- a/data/trans_bre/P12_1_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P12_1_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 6,83</t>
+          <t>0,17; 7,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,48; 16,96</t>
+          <t>9,3; 16,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 10,6</t>
+          <t>2,03; 9,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 12,25</t>
+          <t>4,34; 11,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 33,77</t>
+          <t>0,29; 33,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,02; 100,82</t>
+          <t>44,9; 99,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 59,89</t>
+          <t>10,01; 59,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,43; 77,64</t>
+          <t>21,18; 75,58</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 8,73</t>
+          <t>3,21; 8,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,57</t>
+          <t>6,22; 11,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,89</t>
+          <t>1,64; 5,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 34,93</t>
+          <t>4,3; 32,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,25; 67,58</t>
+          <t>19,36; 65,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,53; 83,53</t>
+          <t>38,55; 83,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,88; 66,85</t>
+          <t>16,43; 65,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,05; 338,0</t>
+          <t>35,29; 333,56</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 9,81</t>
+          <t>-0,69; 9,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 8,08</t>
+          <t>-1,68; 8,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 8,68</t>
+          <t>0,62; 8,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 7,71</t>
+          <t>0,76; 8,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 77,74</t>
+          <t>-4,4; 72,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 73,7</t>
+          <t>-11,46; 73,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 120,42</t>
+          <t>4,37; 112,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 68,29</t>
+          <t>4,98; 74,2</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 7,31</t>
+          <t>3,65; 7,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,22; 12,03</t>
+          <t>8,04; 12,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 6,77</t>
+          <t>3,17; 6,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 28,24</t>
+          <t>5,65; 25,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,77; 45,95</t>
+          <t>20,35; 46,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,33; 81,51</t>
+          <t>48,6; 82,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,51; 62,24</t>
+          <t>24,97; 61,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,69; 277,2</t>
+          <t>42,65; 231,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P12_1_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P12_1_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,28</t>
+          <t>9,3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>54,51%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 7,03</t>
+          <t>-0,23; 6,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,3; 16,6</t>
+          <t>9,2; 16,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 9,86</t>
+          <t>2,13; 10,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 11,89</t>
+          <t>5,3; 12,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 33,76</t>
+          <t>-1,21; 33,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,9; 99,27</t>
+          <t>44,55; 97,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,01; 59,01</t>
+          <t>9,6; 58,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,18; 75,58</t>
+          <t>27,59; 86,6</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,14</t>
+          <t>5,16</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>117,13%</t>
+          <t>41,7%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 8,73</t>
+          <t>3,58; 9,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,22; 11,68</t>
+          <t>6,45; 11,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,65</t>
+          <t>1,59; 5,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 32,23</t>
+          <t>3,22; 7,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,36; 65,9</t>
+          <t>23,13; 70,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,55; 83,99</t>
+          <t>40,1; 88,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,43; 65,73</t>
+          <t>15,03; 65,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,29; 333,56</t>
+          <t>23,67; 64,98</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,32</t>
+          <t>4,11</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 9,19</t>
+          <t>-0,75; 9,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 8,09</t>
+          <t>-1,87; 8,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 8,5</t>
+          <t>0,22; 8,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 8,22</t>
+          <t>0,74; 7,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 72,28</t>
+          <t>-4,8; 72,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 73,08</t>
+          <t>-12,12; 77,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,37; 112,69</t>
+          <t>-0,37; 115,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 74,2</t>
+          <t>4,06; 66,5</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,91</t>
+          <t>6,13</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>45,8%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,42</t>
+          <t>3,38; 7,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,04; 12,11</t>
+          <t>8,07; 12,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,79</t>
+          <t>3,37; 6,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 25,83</t>
+          <t>4,48; 7,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,35; 46,14</t>
+          <t>19,08; 46,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,6; 82,06</t>
+          <t>48,36; 80,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,97; 61,83</t>
+          <t>26,09; 62,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,65; 231,06</t>
+          <t>30,7; 63,04</t>
         </is>
       </c>
     </row>
